--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484229_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484229_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.5175</v>
+        <v>4.1907</v>
       </c>
       <c r="E2" t="n">
         <v>2.2283</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2893</v>
+        <v>1.9624</v>
       </c>
       <c r="G2" t="n">
         <v>0.1972</v>
@@ -610,13 +610,13 @@
         <v>2.7348</v>
       </c>
       <c r="S2" t="n">
-        <v>1.0393</v>
+        <v>0.7125</v>
       </c>
       <c r="T2" t="n">
         <v>0.0167</v>
       </c>
       <c r="U2" t="n">
-        <v>1.0226</v>
+        <v>0.6958</v>
       </c>
       <c r="V2" t="n">
         <v>1.7182</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.0907</v>
+        <v>2.7485</v>
       </c>
       <c r="E3" t="n">
-        <v>2.9594</v>
+        <v>2.4538</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1313</v>
+        <v>0.2947</v>
       </c>
       <c r="G3" t="n">
         <v>2.5249</v>
@@ -688,13 +688,13 @@
         <v>2.7348</v>
       </c>
       <c r="S3" t="n">
-        <v>1.0114</v>
+        <v>0.6692</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9329</v>
+        <v>0.4273</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0785</v>
+        <v>0.2419</v>
       </c>
       <c r="V3" t="n">
         <v>-0.0549</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3285</v>
+        <v>2.1453</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.3807</v>
+        <v>0.3271</v>
       </c>
       <c r="F4" t="n">
-        <v>1.7092</v>
+        <v>1.8181</v>
       </c>
       <c r="G4" t="n">
         <v>1.6276</v>
@@ -766,13 +766,13 @@
         <v>2.5395</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.9316</v>
+        <v>-0.1149</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.1499</v>
+        <v>-0.4421</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2183</v>
+        <v>0.3272</v>
       </c>
       <c r="V4" t="n">
         <v>1.2186</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0646</v>
+        <v>0.8974</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.4442</v>
+        <v>-0.7475000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>1.5087</v>
+        <v>1.6449</v>
       </c>
       <c r="G5" t="n">
         <v>3.6115</v>
@@ -844,13 +844,13 @@
         <v>2.5395</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1375</v>
+        <v>-0.0296</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3193</v>
+        <v>0.016</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1818</v>
+        <v>-0.0456</v>
       </c>
       <c r="V5" t="n">
         <v>0.8317</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. PORTALEZ MUR</t>
+          <t>D. MELINTE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3996</v>
+        <v>-0.4047</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.3423</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1.742</v>
+        <v>-0.4047</v>
       </c>
       <c r="G6" t="n">
-        <v>1.9823</v>
+        <v>-0.4047</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5262</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>2.5085</v>
+        <v>-0.4047</v>
       </c>
       <c r="J6" t="n">
-        <v>3.0458</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5359</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>2.5099</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.0635</v>
+        <v>-0.4047</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.0621</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0014</v>
+        <v>-0.4047</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.3441</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-5.0789</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.7348</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1.9253</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6908</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.2345</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.1638</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.1638</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. MELINTE</t>
+          <t>M. PORTALEZ MUR</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4047</v>
+        <v>-0.5689</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>-1.8479</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.4047</v>
+        <v>1.279</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.4047</v>
+        <v>1.9823</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>-0.5262</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4047</v>
+        <v>2.5085</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>3.0458</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>0.5359</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.5099</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4047</v>
+        <v>-1.0635</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>-1.0621</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4047</v>
+        <v>-0.0014</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-2.3441</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-5.0789</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.7348</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>0.9567</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>0.1852</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>0.7715</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-1.1638</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.1638</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.7877</v>
+        <v>-2.7997</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.7384</v>
+        <v>-3.1317</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0493</v>
+        <v>0.332</v>
       </c>
       <c r="G9" t="n">
         <v>-0.721</v>
@@ -1156,13 +1156,13 @@
         <v>0.3907</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5272</v>
+        <v>0.4608</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7262999999999999</v>
+        <v>-0.1196</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1991</v>
+        <v>0.5804</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>5.803800000000001</v>
+        <v>5.8039</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7179000000000002</v>
+        <v>-0.7178999999999993</v>
       </c>
       <c r="F10" t="n">
-        <v>6.521800000000001</v>
+        <v>6.5217</v>
       </c>
       <c r="G10" t="n">
         <v>8.4131</v>
@@ -1237,7 +1237,7 @@
         <v>2.6547</v>
       </c>
       <c r="T10" t="n">
-        <v>0.08350000000000002</v>
+        <v>0.08350000000000003</v>
       </c>
       <c r="U10" t="n">
         <v>2.5712</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>3.9426</v>
+        <v>3.0325</v>
       </c>
       <c r="E11" t="n">
-        <v>2.4645</v>
+        <v>1.5545</v>
       </c>
       <c r="F11" t="n">
         <v>1.478</v>
@@ -1312,10 +1312,10 @@
         <v>3.5162</v>
       </c>
       <c r="S11" t="n">
-        <v>0.8778</v>
+        <v>-0.0322</v>
       </c>
       <c r="T11" t="n">
-        <v>0.6441</v>
+        <v>-0.266</v>
       </c>
       <c r="U11" t="n">
         <v>0.2337</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>F. ALVAREZ BACO</t>
+          <t>J. BERTOMEU BALDÉ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,58 +1345,58 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>1.4596</v>
+        <v>1.8737</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3243</v>
+        <v>1.4377</v>
       </c>
       <c r="F12" t="n">
-        <v>1.1353</v>
+        <v>0.4361</v>
       </c>
       <c r="G12" t="n">
-        <v>0.4641</v>
+        <v>1.9831</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.5191</v>
+        <v>0.3106</v>
       </c>
       <c r="I12" t="n">
-        <v>1.9832</v>
+        <v>1.6725</v>
       </c>
       <c r="J12" t="n">
-        <v>0.4837</v>
+        <v>2.3325</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.6908</v>
+        <v>1.0642</v>
       </c>
       <c r="L12" t="n">
-        <v>1.1745</v>
+        <v>1.2683</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.0196</v>
+        <v>-0.3494</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.8283</v>
+        <v>-0.7536</v>
       </c>
       <c r="O12" t="n">
-        <v>0.8087</v>
+        <v>0.4043</v>
       </c>
       <c r="P12" t="n">
-        <v>1.9534</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R12" t="n">
-        <v>1.9534</v>
+        <v>0.9767</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9579</v>
+        <v>-0.1094</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1594</v>
+        <v>0.0819</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.7985</v>
+        <v>-0.1913</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. BERTOMEU BALDÉ</t>
+          <t>F. ALVAREZ BACO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,58 +1423,58 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.3409</v>
+        <v>1.6775</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9321</v>
+        <v>0.3243</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4088</v>
+        <v>1.3532</v>
       </c>
       <c r="G13" t="n">
-        <v>1.9831</v>
+        <v>0.4641</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3106</v>
+        <v>-1.5191</v>
       </c>
       <c r="I13" t="n">
-        <v>1.6725</v>
+        <v>1.9832</v>
       </c>
       <c r="J13" t="n">
-        <v>2.3325</v>
+        <v>0.4837</v>
       </c>
       <c r="K13" t="n">
-        <v>1.0642</v>
+        <v>-0.6908</v>
       </c>
       <c r="L13" t="n">
-        <v>1.2683</v>
+        <v>1.1745</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.3494</v>
+        <v>-0.0196</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.7536</v>
+        <v>-0.8283</v>
       </c>
       <c r="O13" t="n">
-        <v>0.4043</v>
+        <v>0.8087</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.9534</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0.9767</v>
+        <v>1.9534</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6422</v>
+        <v>-0.74</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4237</v>
+        <v>-0.1594</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2185</v>
+        <v>-0.5806</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. FONTANALS MARTIN</t>
+          <t>G. LOZANO MASSANET</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2762</v>
+        <v>0.9167999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>1.3703</v>
+        <v>1.9936</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.0941</v>
+        <v>-1.0769</v>
       </c>
       <c r="G14" t="n">
-        <v>-2.931</v>
+        <v>1.2668</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.4879</v>
+        <v>-2.1464</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.4431</v>
+        <v>3.4131</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.125</v>
+        <v>2.44</v>
       </c>
       <c r="K14" t="n">
-        <v>1.0476</v>
+        <v>-0.5692</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.1725</v>
+        <v>3.0093</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.8061</v>
+        <v>-1.1733</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.5354</v>
+        <v>-1.5771</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.2706</v>
+        <v>0.4039</v>
       </c>
       <c r="P14" t="n">
-        <v>1.7581</v>
+        <v>0.3907</v>
       </c>
       <c r="Q14" t="n">
         <v>-1.1721</v>
       </c>
       <c r="R14" t="n">
-        <v>2.9301</v>
+        <v>1.5627</v>
       </c>
       <c r="S14" t="n">
-        <v>0.8398</v>
+        <v>-0.1314</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8394</v>
+        <v>0.1164</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0004</v>
+        <v>-0.2477</v>
       </c>
       <c r="V14" t="n">
+        <v>-0.6093</v>
+      </c>
+      <c r="W14" t="n">
         <v>0.6093</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.8279</v>
       </c>
       <c r="X14" t="n">
         <v>-1.2186</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2095</v>
+        <v>-0.2184</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9708</v>
+        <v>0.8697</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.7613</v>
+        <v>-1.0881</v>
       </c>
       <c r="G15" t="n">
         <v>-0.6428</v>
@@ -1624,13 +1624,13 @@
         <v>1.3674</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4616</v>
+        <v>0.0337</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0083</v>
+        <v>-0.09279999999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4533</v>
+        <v>0.1265</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. LOZANO MASSANET</t>
+          <t>M. FONTANALS MARTIN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1545</v>
+        <v>-0.3771</v>
       </c>
       <c r="E16" t="n">
-        <v>1.2858</v>
+        <v>0.6625</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.1314</v>
+        <v>-1.0397</v>
       </c>
       <c r="G16" t="n">
-        <v>1.2668</v>
+        <v>-2.931</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.1464</v>
+        <v>-1.4879</v>
       </c>
       <c r="I16" t="n">
-        <v>3.4131</v>
+        <v>-1.4431</v>
       </c>
       <c r="J16" t="n">
-        <v>2.44</v>
+        <v>-0.125</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.5692</v>
+        <v>1.0476</v>
       </c>
       <c r="L16" t="n">
-        <v>3.0093</v>
+        <v>-1.1725</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.1733</v>
+        <v>-2.8061</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.5771</v>
+        <v>-2.5354</v>
       </c>
       <c r="O16" t="n">
-        <v>0.4039</v>
+        <v>-0.2706</v>
       </c>
       <c r="P16" t="n">
-        <v>0.3907</v>
+        <v>1.7581</v>
       </c>
       <c r="Q16" t="n">
         <v>-1.1721</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5627</v>
+        <v>2.9301</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.8937</v>
+        <v>0.1865</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5915</v>
+        <v>0.1316</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3022</v>
+        <v>0.0549</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.6093</v>
+        <v>0.6093</v>
       </c>
       <c r="W16" t="n">
-        <v>0.6093</v>
+        <v>1.8279</v>
       </c>
       <c r="X16" t="n">
         <v>-1.2186</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. TOLEDO CIVICO</t>
+          <t>M. GARCIA LOPEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.2666</v>
+        <v>-1.2406</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.6247</v>
+        <v>-0.3614</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3581</v>
+        <v>-0.8792</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.4853</v>
+        <v>-0.5515</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0542</v>
+        <v>-0.9558</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.5395</v>
+        <v>0.4043</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.3454</v>
+        <v>0.8119</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3287</v>
+        <v>0.0025</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6741</v>
+        <v>0.8093</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.1399</v>
+        <v>-1.3634</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2745</v>
+        <v>-0.9583</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1346</v>
+        <v>-0.4051</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.7814</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q17" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R17" t="n">
-        <v>0.1953</v>
+        <v>0.586</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>0.0337</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3026</v>
+        <v>0.1356</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3026</v>
+        <v>-0.1018</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.3321</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>-0.3321</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R. DALET CASALPRIM</t>
+          <t>M. TOLEDO CIVICO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.4535</v>
+        <v>-1.2666</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.3743</v>
+        <v>-1.6247</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.07920000000000001</v>
+        <v>0.3581</v>
       </c>
       <c r="G18" t="n">
-        <v>1.4627</v>
+        <v>-0.4853</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9775</v>
+        <v>0.0542</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4852</v>
+        <v>-0.5395</v>
       </c>
       <c r="J18" t="n">
-        <v>1.0633</v>
+        <v>-0.3454</v>
       </c>
       <c r="K18" t="n">
-        <v>0.9824000000000001</v>
+        <v>0.3287</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0809</v>
+        <v>-0.6741</v>
       </c>
       <c r="M18" t="n">
-        <v>0.3994</v>
+        <v>-0.1399</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0049</v>
+        <v>-0.2745</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4043</v>
+        <v>0.1346</v>
       </c>
       <c r="P18" t="n">
+        <v>-0.7814</v>
+      </c>
+      <c r="Q18" t="n">
         <v>-0.9767</v>
       </c>
-      <c r="Q18" t="n">
-        <v>-1.9534</v>
-      </c>
       <c r="R18" t="n">
-        <v>0.9767</v>
+        <v>0.1953</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7208</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4842</v>
+        <v>-0.3026</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2367</v>
+        <v>0.3026</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. LLORENTE GUILLEMI</t>
+          <t>R. DALET CASALPRIM</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.4935</v>
+        <v>-1.3524</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.7541</v>
+        <v>-1.2732</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2606</v>
+        <v>-0.07920000000000001</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.9772</v>
+        <v>1.4627</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.7897</v>
+        <v>0.9775</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.1875</v>
+        <v>0.4852</v>
       </c>
       <c r="J19" t="n">
-        <v>1.2887</v>
+        <v>1.0633</v>
       </c>
       <c r="K19" t="n">
-        <v>1.1269</v>
+        <v>0.9824000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1619</v>
+        <v>0.0809</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.266</v>
+        <v>0.3994</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.9166</v>
+        <v>-0.0049</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.3494</v>
+        <v>0.4043</v>
       </c>
       <c r="P19" t="n">
-        <v>0.1953</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.1488</v>
+        <v>-1.9534</v>
       </c>
       <c r="R19" t="n">
-        <v>2.3441</v>
+        <v>0.9767</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0985</v>
+        <v>-0.6197</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8941</v>
+        <v>-0.3831</v>
       </c>
       <c r="U19" t="n">
-        <v>0.7956</v>
+        <v>-0.2367</v>
       </c>
       <c r="V19" t="n">
-        <v>0.3869</v>
+        <v>-1.2186</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.3869</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. GARCIA LOPEZ</t>
+          <t>J. LLORENTE GUILLEMI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.5439</v>
+        <v>-1.408</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.6647</v>
+        <v>-1.4507</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.8792</v>
+        <v>0.0427</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.5515</v>
+        <v>-1.9772</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.9558</v>
+        <v>-0.7897</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4043</v>
+        <v>-1.1875</v>
       </c>
       <c r="J20" t="n">
-        <v>0.8119</v>
+        <v>1.2887</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0025</v>
+        <v>1.1269</v>
       </c>
       <c r="L20" t="n">
-        <v>0.8093</v>
+        <v>0.1619</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.3634</v>
+        <v>-3.266</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.9583</v>
+        <v>-1.9166</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.4051</v>
+        <v>-1.3494</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.3907</v>
+        <v>0.1953</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9767</v>
+        <v>-2.1488</v>
       </c>
       <c r="R20" t="n">
-        <v>0.586</v>
+        <v>2.3441</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2696</v>
+        <v>-0.013</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1678</v>
+        <v>-0.5907</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1018</v>
+        <v>0.5777</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.3321</v>
+        <v>0.3869</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>0.3869</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.5143</v>
+        <v>-2.946</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.0765</v>
+        <v>-4.4809</v>
       </c>
       <c r="F21" t="n">
-        <v>1.5622</v>
+        <v>1.5349</v>
       </c>
       <c r="G21" t="n">
         <v>-2.9597</v>
@@ -2092,13 +2092,13 @@
         <v>2.1488</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1722</v>
+        <v>-0.6039</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.22</v>
+        <v>-0.6244</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0478</v>
+        <v>0.0206</v>
       </c>
       <c r="V21" t="n">
         <v>-0.5545</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.9155</v>
+        <v>-4.4954</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.6527</v>
+        <v>-4.4505</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.2628</v>
+        <v>-0.0449</v>
       </c>
       <c r="G22" t="n">
         <v>-3.7314</v>
@@ -2170,13 +2170,13 @@
         <v>2.9301</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.079</v>
+        <v>-0.6589</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8198</v>
+        <v>-0.6175</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2592</v>
+        <v>-0.0413</v>
       </c>
       <c r="V22" t="n">
         <v>-0.8865</v>
@@ -2206,10 +2206,10 @@
         <v>-5.804</v>
       </c>
       <c r="E23" t="n">
-        <v>-6.7992</v>
+        <v>-6.7991</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9949999999999997</v>
+        <v>0.9949999999999996</v>
       </c>
       <c r="G23" t="n">
         <v>-8.4131</v>
@@ -2218,10 +2218,10 @@
         <v>-8.414099999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>0.001000000000000334</v>
+        <v>0.0009999999999994458</v>
       </c>
       <c r="J23" t="n">
-        <v>7.340700000000003</v>
+        <v>7.340700000000001</v>
       </c>
       <c r="K23" t="n">
         <v>5.310600000000001</v>
@@ -2248,13 +2248,13 @@
         <v>21.4875</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.6547</v>
+        <v>-2.6546</v>
       </c>
       <c r="T23" t="n">
-        <v>-2.5713</v>
+        <v>-2.571</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.08349999999999996</v>
+        <v>-0.08340000000000009</v>
       </c>
       <c r="V23" t="n">
         <v>-2.5499</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484229_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484229_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X23"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484229_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484229_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484229_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484229_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484229_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484229_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.1638</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484229_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484229_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,7 @@
       <c r="X10" t="n">
         <v>-2.3824</v>
       </c>
+      <c r="Y10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1260,7 +1306,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1328,75 +1374,80 @@
       </c>
       <c r="X11" t="n">
         <v>0.0549</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484229_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. BERTOMEU BALDÉ</t>
+          <t>F. ALVAREZ BACO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>1.8737</v>
+        <v>1.6775</v>
       </c>
       <c r="E12" t="n">
-        <v>1.4377</v>
+        <v>0.3243</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4361</v>
+        <v>1.3532</v>
       </c>
       <c r="G12" t="n">
-        <v>1.9831</v>
+        <v>0.4641</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3106</v>
+        <v>-1.5191</v>
       </c>
       <c r="I12" t="n">
-        <v>1.6725</v>
+        <v>1.9832</v>
       </c>
       <c r="J12" t="n">
-        <v>2.3325</v>
+        <v>0.4837</v>
       </c>
       <c r="K12" t="n">
-        <v>1.0642</v>
+        <v>-0.6908</v>
       </c>
       <c r="L12" t="n">
-        <v>1.2683</v>
+        <v>1.1745</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.3494</v>
+        <v>-0.0196</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.7536</v>
+        <v>-0.8283</v>
       </c>
       <c r="O12" t="n">
-        <v>0.4043</v>
+        <v>0.8087</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.9534</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.9767</v>
+        <v>1.9534</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1094</v>
+        <v>-0.74</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0819</v>
+        <v>-0.1594</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1913</v>
+        <v>-0.5806</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1406,75 +1457,80 @@
       </c>
       <c r="X12" t="n">
         <v>0</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484229_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>F. ALVAREZ BACO</t>
+          <t>J. BERTOMEU BALDE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.6775</v>
+        <v>1.2667</v>
       </c>
       <c r="E13" t="n">
-        <v>0.3243</v>
+        <v>0.8307</v>
       </c>
       <c r="F13" t="n">
-        <v>1.3532</v>
+        <v>0.4361</v>
       </c>
       <c r="G13" t="n">
-        <v>0.4641</v>
+        <v>1.3761</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.5191</v>
+        <v>0.3106</v>
       </c>
       <c r="I13" t="n">
-        <v>1.9832</v>
+        <v>1.0655</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4837</v>
+        <v>1.7255</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.6908</v>
+        <v>1.0642</v>
       </c>
       <c r="L13" t="n">
-        <v>1.1745</v>
+        <v>0.6613</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.0196</v>
+        <v>-0.3494</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.8283</v>
+        <v>-0.7536</v>
       </c>
       <c r="O13" t="n">
-        <v>0.8087</v>
+        <v>0.4043</v>
       </c>
       <c r="P13" t="n">
-        <v>1.9534</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R13" t="n">
-        <v>1.9534</v>
+        <v>0.9767</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.74</v>
+        <v>-0.1094</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1594</v>
+        <v>0.0819</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5806</v>
+        <v>-0.1913</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1484,6 +1540,11 @@
       </c>
       <c r="X13" t="n">
         <v>0</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484229_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -1494,7 +1555,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1562,6 +1623,11 @@
       </c>
       <c r="X14" t="n">
         <v>-1.2186</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484229_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -1572,65 +1638,65 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.2184</v>
+        <v>0.914</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8697</v>
+        <v>0.914</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.0881</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.6428</v>
+        <v>0.914</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6117</v>
+        <v>0.307</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.2544</v>
+        <v>0.607</v>
       </c>
       <c r="J15" t="n">
-        <v>1.9392</v>
+        <v>0.914</v>
       </c>
       <c r="K15" t="n">
-        <v>1.8445</v>
+        <v>0.307</v>
       </c>
       <c r="L15" t="n">
-        <v>0.09470000000000001</v>
+        <v>0.607</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.582</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.2328</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.3492</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>0.3907</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3674</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0337</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.09279999999999999</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1265</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1640,631 +1706,921 @@
       </c>
       <c r="X15" t="n">
         <v>0</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484229_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. FONTANALS MARTIN</t>
+          <t>J. BERTOMEU BALDÉ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.3771</v>
+        <v>0.607</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6625</v>
+        <v>0.607</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.0397</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.931</v>
+        <v>0.607</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.4879</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.4431</v>
+        <v>0.607</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.125</v>
+        <v>0.607</v>
       </c>
       <c r="K16" t="n">
-        <v>1.0476</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.1725</v>
+        <v>0.607</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.8061</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.5354</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2706</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.7581</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1721</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.9301</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1865</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1316</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0549</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>0.6093</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.8279</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484229_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. GARCIA LOPEZ</t>
+          <t>R. PALOMARES MUÑOZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.2406</v>
+        <v>0.307</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.3614</v>
+        <v>0.307</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.8792</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.5515</v>
+        <v>0.307</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.9558</v>
+        <v>0.307</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4043</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8119</v>
+        <v>0.307</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0025</v>
+        <v>0.307</v>
       </c>
       <c r="L17" t="n">
-        <v>0.8093</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.3634</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.9583</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.4051</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.3907</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0337</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1356</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1018</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484229_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. TOLEDO CIVICO</t>
+          <t>M. FONTANALS MARTIN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.2666</v>
+        <v>-0.3771</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.6247</v>
+        <v>0.6625</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3581</v>
+        <v>-1.0397</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.4853</v>
+        <v>-2.931</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0542</v>
+        <v>-1.4879</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.5395</v>
+        <v>-1.4431</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.3454</v>
+        <v>-0.125</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3287</v>
+        <v>1.0476</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.6741</v>
+        <v>-1.1725</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.1399</v>
+        <v>-2.8061</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2745</v>
+        <v>-2.5354</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1346</v>
+        <v>-0.2706</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.7814</v>
+        <v>1.7581</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9767</v>
+        <v>-1.1721</v>
       </c>
       <c r="R18" t="n">
-        <v>0.1953</v>
+        <v>2.9301</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>0.1865</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3026</v>
+        <v>0.1316</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3026</v>
+        <v>0.0549</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.6093</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.8279</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484229_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R. DALET CASALPRIM</t>
+          <t>E. MARTIN GASCON</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.3524</v>
+        <v>-1.1324</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.2732</v>
+        <v>-0.0442</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.07920000000000001</v>
+        <v>-1.0881</v>
       </c>
       <c r="G19" t="n">
-        <v>1.4627</v>
+        <v>-1.5568</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9775</v>
+        <v>0.3047</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4852</v>
+        <v>-1.8614</v>
       </c>
       <c r="J19" t="n">
-        <v>1.0633</v>
+        <v>1.0252</v>
       </c>
       <c r="K19" t="n">
-        <v>0.9824000000000001</v>
+        <v>1.5375</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0809</v>
+        <v>-0.5122</v>
       </c>
       <c r="M19" t="n">
-        <v>0.3994</v>
+        <v>-2.582</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0049</v>
+        <v>-1.2328</v>
       </c>
       <c r="O19" t="n">
-        <v>0.4043</v>
+        <v>-1.3492</v>
       </c>
       <c r="P19" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="Q19" t="n">
         <v>-0.9767</v>
       </c>
-      <c r="Q19" t="n">
-        <v>-1.9534</v>
-      </c>
       <c r="R19" t="n">
-        <v>0.9767</v>
+        <v>1.3674</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6197</v>
+        <v>0.0337</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3831</v>
+        <v>-0.09279999999999999</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2367</v>
+        <v>0.1265</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484229_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. LLORENTE GUILLEMI</t>
+          <t>M. GARCIA LOPEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.408</v>
+        <v>-1.2406</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.4507</v>
+        <v>-0.3614</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0427</v>
+        <v>-0.8792</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.9772</v>
+        <v>-0.5515</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.7897</v>
+        <v>-0.9558</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.1875</v>
+        <v>0.4043</v>
       </c>
       <c r="J20" t="n">
-        <v>1.2887</v>
+        <v>0.8119</v>
       </c>
       <c r="K20" t="n">
-        <v>1.1269</v>
+        <v>0.0025</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1619</v>
+        <v>0.8093</v>
       </c>
       <c r="M20" t="n">
-        <v>-3.266</v>
+        <v>-1.3634</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.9166</v>
+        <v>-0.9583</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.3494</v>
+        <v>-0.4051</v>
       </c>
       <c r="P20" t="n">
-        <v>0.1953</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.1488</v>
+        <v>-0.9767</v>
       </c>
       <c r="R20" t="n">
-        <v>2.3441</v>
+        <v>0.586</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.013</v>
+        <v>0.0337</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5907</v>
+        <v>0.1356</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5777</v>
+        <v>-0.1018</v>
       </c>
       <c r="V20" t="n">
-        <v>0.3869</v>
+        <v>-0.3321</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>-0.3321</v>
       </c>
       <c r="X20" t="n">
-        <v>0.3869</v>
+        <v>0</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484229_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R. PALOMARES MUÑOZ</t>
+          <t>M. TOLEDO CIVICO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.946</v>
+        <v>-1.2666</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.4809</v>
+        <v>-1.6247</v>
       </c>
       <c r="F21" t="n">
-        <v>1.5349</v>
+        <v>0.3581</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.9597</v>
+        <v>-0.4853</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.7864</v>
+        <v>0.0542</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.1733</v>
+        <v>-0.5395</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.8798</v>
+        <v>-0.3454</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.5721</v>
+        <v>0.3287</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.3077</v>
+        <v>-0.6741</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.0799</v>
+        <v>-0.1399</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2144</v>
+        <v>-0.2745</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1344</v>
+        <v>0.1346</v>
       </c>
       <c r="P21" t="n">
-        <v>1.1721</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q21" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R21" t="n">
-        <v>2.1488</v>
+        <v>0.1953</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6039</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6244</v>
+        <v>-0.3026</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0206</v>
+        <v>0.3026</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484229_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R. FERNANDEZ DIAZ</t>
+          <t>R. DALET CASALPRIM</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.4954</v>
+        <v>-1.3524</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.4505</v>
+        <v>-1.2732</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.0449</v>
+        <v>-0.07920000000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.7314</v>
+        <v>1.4627</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.9811</v>
+        <v>0.9775</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.7503</v>
+        <v>0.4852</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.6842</v>
+        <v>1.0633</v>
       </c>
       <c r="K22" t="n">
-        <v>0.3914</v>
+        <v>0.9824000000000001</v>
       </c>
       <c r="L22" t="n">
-        <v>-2.0756</v>
+        <v>0.0809</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.0472</v>
+        <v>0.3994</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.3725</v>
+        <v>-0.0049</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.6747</v>
+        <v>0.4043</v>
       </c>
       <c r="P22" t="n">
-        <v>0.7814</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.1488</v>
+        <v>-1.9534</v>
       </c>
       <c r="R22" t="n">
-        <v>2.9301</v>
+        <v>0.9767</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6589</v>
+        <v>-0.6197</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6175</v>
+        <v>-0.3831</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0413</v>
+        <v>-0.2367</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.8865</v>
+        <v>-1.2186</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.8865</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484229_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>J. LLORENTE GUILLEMI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>1</v>
       </c>
       <c r="D23" t="n">
+        <v>-1.408</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-1.4507</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.0427</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-1.9772</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-0.7897</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-1.1875</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.2887</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1.1269</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.1619</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-3.266</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-1.9166</v>
+      </c>
+      <c r="O23" t="n">
+        <v>-1.3494</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.1953</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>-2.1488</v>
+      </c>
+      <c r="R23" t="n">
+        <v>2.3441</v>
+      </c>
+      <c r="S23" t="n">
+        <v>-0.013</v>
+      </c>
+      <c r="T23" t="n">
+        <v>-0.5907</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0.5777</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0.3869</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0.3869</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484229_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>R. PALOMARES MUNOZ</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-3.253</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-4.7879</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.5349</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-3.2667</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-2.0934</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-1.1733</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-3.1868</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-1.879</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-1.3077</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-0.0799</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-0.2144</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.1344</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.1721</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R24" t="n">
+        <v>2.1488</v>
+      </c>
+      <c r="S24" t="n">
+        <v>-0.6039</v>
+      </c>
+      <c r="T24" t="n">
+        <v>-0.6244</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.0206</v>
+      </c>
+      <c r="V24" t="n">
+        <v>-0.5545</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>-0.5545</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484229_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>R. FERNANDEZ DIAZ</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-4.4954</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-4.4505</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-0.0449</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-3.7314</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-0.9811</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-2.7503</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-1.6842</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.3914</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-2.0756</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-2.0472</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-1.3725</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-0.6747</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0.7814</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-2.1488</v>
+      </c>
+      <c r="R25" t="n">
+        <v>2.9301</v>
+      </c>
+      <c r="S25" t="n">
+        <v>-0.6589</v>
+      </c>
+      <c r="T25" t="n">
+        <v>-0.6175</v>
+      </c>
+      <c r="U25" t="n">
+        <v>-0.0413</v>
+      </c>
+      <c r="V25" t="n">
+        <v>-0.8865</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>-0.8865</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484229_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
         <v>-5.804</v>
       </c>
-      <c r="E23" t="n">
-        <v>-6.7991</v>
-      </c>
-      <c r="F23" t="n">
+      <c r="E26" t="n">
+        <v>-6.798999999999999</v>
+      </c>
+      <c r="F26" t="n">
         <v>0.9949999999999996</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G26" t="n">
         <v>-8.4131</v>
       </c>
-      <c r="H23" t="n">
+      <c r="H26" t="n">
         <v>-8.414099999999999</v>
       </c>
-      <c r="I23" t="n">
-        <v>0.0009999999999994458</v>
-      </c>
-      <c r="J23" t="n">
+      <c r="I26" t="n">
+        <v>0.001000000000000334</v>
+      </c>
+      <c r="J26" t="n">
         <v>7.340700000000001</v>
       </c>
-      <c r="K23" t="n">
-        <v>5.310600000000001</v>
-      </c>
-      <c r="L23" t="n">
-        <v>2.0303</v>
-      </c>
-      <c r="M23" t="n">
+      <c r="K26" t="n">
+        <v>5.3107</v>
+      </c>
+      <c r="L26" t="n">
+        <v>2.0304</v>
+      </c>
+      <c r="M26" t="n">
         <v>-15.7541</v>
       </c>
-      <c r="N23" t="n">
+      <c r="N26" t="n">
         <v>-13.7247</v>
       </c>
-      <c r="O23" t="n">
-        <v>-2.0292</v>
-      </c>
-      <c r="P23" t="n">
+      <c r="O26" t="n">
+        <v>-2.029199999999999</v>
+      </c>
+      <c r="P26" t="n">
         <v>7.813699999999999</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="Q26" t="n">
         <v>-13.674</v>
       </c>
-      <c r="R23" t="n">
+      <c r="R26" t="n">
         <v>21.4875</v>
       </c>
-      <c r="S23" t="n">
+      <c r="S26" t="n">
         <v>-2.6546</v>
       </c>
-      <c r="T23" t="n">
+      <c r="T26" t="n">
         <v>-2.571</v>
       </c>
-      <c r="U23" t="n">
+      <c r="U26" t="n">
         <v>-0.08340000000000009</v>
       </c>
-      <c r="V23" t="n">
+      <c r="V26" t="n">
         <v>-2.5499</v>
       </c>
-      <c r="W23" t="n">
+      <c r="W26" t="n">
         <v>2.1051</v>
       </c>
-      <c r="X23" t="n">
+      <c r="X26" t="n">
         <v>-4.654999999999999</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
